--- a/data/Descriptive of the variables.xlsx
+++ b/data/Descriptive of the variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Josep Lledó\Dropbox\Ciencias Sociales\Jorge tesis\Paper Datos\EAJ\Revision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/023bd6fa9390373a/Desktop/takmicenje/isurance_vezba/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C679E5E-1EB0-4706-BDB9-456CBC2FD1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B720401-42BD-4127-ACEB-1F5D8FF679CD}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{9B720401-42BD-4127-ACEB-1F5D8FF679CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Motor vehicle insurance data" sheetId="1" r:id="rId1"/>
@@ -346,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -370,7 +370,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -398,7 +397,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -695,13 +694,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEC570A2-8FED-4B18-AA9F-1B6F95F8C81B}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="75.140625" customWidth="1"/>
+    <col min="2" max="2" width="75.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -709,7 +708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -717,7 +716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -725,7 +724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -733,7 +732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -741,7 +740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -749,7 +748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -757,7 +756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -765,7 +764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -773,7 +772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -781,7 +780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
@@ -789,7 +788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -797,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>24</v>
       </c>
@@ -805,7 +804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
@@ -813,7 +812,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
@@ -821,7 +820,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>30</v>
       </c>
@@ -829,7 +828,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
@@ -837,7 +836,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -845,7 +844,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
@@ -853,7 +852,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>38</v>
       </c>
@@ -861,7 +860,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>40</v>
       </c>
@@ -869,7 +868,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>42</v>
       </c>
@@ -877,7 +876,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>44</v>
       </c>
@@ -885,7 +884,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>46</v>
       </c>
@@ -893,7 +892,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -901,7 +900,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -909,7 +908,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -917,7 +916,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -925,7 +924,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -933,7 +932,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>58</v>
       </c>
@@ -941,7 +940,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>60</v>
       </c>
@@ -957,13 +956,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87061B0-29F5-4654-BC6B-03AF71D07DB7}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="126.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -971,35 +970,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:2" ht="25.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>66</v>
       </c>
     </row>
